--- a/Lab/Employee Details.xlsx
+++ b/Lab/Employee Details.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1" spans="1:10">
